--- a/tests/fixtures/lom/1004611-1-LOM.xlsx
+++ b/tests/fixtures/lom/1004611-1-LOM.xlsx
@@ -78,39 +78,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S 80054-1</t>
+          <t>1004612-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10" GASKET</t>
+          <t>24 X 30 PLATFORM WELDMENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1004675-1</t>
+          <t>15062-2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -122,25 +122,565 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40002-8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>44013-7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>42005-1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>89047-1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3649-7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>89028-1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>48049-1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>40014-1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>42005-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1004065-1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>89134-1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>42005-3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>44013-6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10"</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>80054-1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10" DOOR SEAL GASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1004620-1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12803-1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>44013-3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>40006-7</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>42005-5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1004675-1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>1004620-2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -205,17 +745,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1004612-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>24 X 30 PLATFORM WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15062-2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>40002-8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>44013-7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>42005-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>89047-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3649-7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>89028-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>48049-1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>40014-1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>42005-17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1004065-1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>89134-1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>42005-3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>44013-6</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S 80054-1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10" GASKET</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>80054-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10" DOOR SEAL GASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1004620-1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12803-1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>44013-3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>40006-7</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>42005-5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
